--- a/templates/Software_Observation_Upload_Template.xlsx
+++ b/templates/Software_Observation_Upload_Template.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W1"/>
+  <dimension ref="A1:Y1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -440,6 +440,8 @@
     <col width="22" customWidth="1" min="21" max="21"/>
     <col width="22" customWidth="1" min="22" max="22"/>
     <col width="22" customWidth="1" min="23" max="23"/>
+    <col width="22" customWidth="1" min="24" max="24"/>
+    <col width="22" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -545,15 +547,25 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>Browser version</t>
+          <t>Edge version</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
+          <t>Chrome version</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>Firefox version</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
           <t>Local administrators</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Remarks</t>
         </is>
